--- a/output/training_result_databaru/frequent_itemsets_80_20.xlsx
+++ b/output/training_result_databaru/frequent_itemsets_80_20.xlsx
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Anisa', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'operator_Anisa'})</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb night brightening', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_hb night brightening'})</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'operator_Riska', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'operator_Riska', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket brightening', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_paket brightening'})</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket brightening', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket brightening'})</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket brightening', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_paket brightening'})</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_paket brightening'})</t>
+          <t>frozenset({'produk_paket brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_sunscreen oily acne new'})</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Siang', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_sunscreen oily acne new', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket custom', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket custom'})</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'waktu_Siang', 'produk_night cream brightening'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_night cream brightening', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'operator_Indah', 'produk_night cream brightening'})</t>
+          <t>frozenset({'waktu_Malam', 'produk_night cream brightening', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Indah', 'produk_night cream brightening'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Siang', 'produk_night cream brightening'})</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Indah', 'produk_night cream brightening'})</t>
+          <t>frozenset({'operator_Indah', 'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Oktavira', 'produk_night cream brightening'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_sunscreen glowing new'})</t>
+          <t>frozenset({'produk_sunscreen glowing new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_daily ceramois hydra gel'})</t>
+          <t>frozenset({'produk_daily ceramois hydra gel', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket radian brightening ultimate', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_facial wash oily acne 110 ml new'})</t>
+          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Riska', 'waktu_Siang'})</t>
+          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'waktu_Siang', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket acne brightening', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket acne brightening'})</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>frozenset({'produk_bb chusion flawless', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_bb chusion flawless'})</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb night yellow plus licorice', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_hb night yellow plus licorice'})</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb night yellow plus licorice', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_hb night yellow plus licorice'})</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
